--- a/output/pdf_financials_xlsx/SMCD.P.xlsx
+++ b/output/pdf_financials_xlsx/SMCD.P.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SMCD.P.xlsx
+++ b/output/pdf_financials_xlsx/SMCD.P.xlsx
@@ -486,8 +486,10 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0.027862</v>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
@@ -819,7 +821,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>0.027862</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>0</v>
@@ -1144,7 +1146,7 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.004042</v>
+        <v>-0.02382</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>0.003462</v>
@@ -1182,7 +1184,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.004042</v>
+        <v>-0.02382</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0.003462</v>
@@ -8295,7 +8297,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">

--- a/output/pdf_financials_xlsx/SMCD.P.xlsx
+++ b/output/pdf_financials_xlsx/SMCD.P.xlsx
@@ -2100,14 +2100,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n">
-        <v>0.006214</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>0.005791</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>0.006231</v>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -2149,13 +2155,13 @@
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>0.777613</v>
+        <v>0.7838270000000001</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.804902</v>
+        <v>0.810693</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.872321</v>
+        <v>0.878552</v>
       </c>
     </row>
     <row r="74">
@@ -4351,7 +4357,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
